--- a/artfynd/A 38170-2021 artfynd.xlsx
+++ b/artfynd/A 38170-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38170-2021 artfynd.xlsx
+++ b/artfynd/A 38170-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,43 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104497532</v>
+        <v>80075934</v>
       </c>
       <c r="B2" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,10 +721,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>569748.7077442128</v>
+        <v>569796</v>
       </c>
       <c r="R2" t="n">
-        <v>6621844.262036867</v>
+        <v>6621930</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -749,22 +751,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2022-10-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2022-10-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-09-24</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -779,7 +771,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Tallskog</t>
+          <t>Tallskog, blåbärsristyp</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>På trampat motionsspår</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,6 +791,227 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>104497574</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93235</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5966</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Motaggsvamp</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sarcodon squamosus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Lindmuren, Vstm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>569796</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6621933</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2022-10-08</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2022-10-08</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>Tallskog, inslag av gran, björk</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>104497532</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97983</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lindmuren, Vstm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>569749</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6621844</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Surahammar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Sura</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-10-08</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-10-08</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Tom Sävström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
